--- a/doc/Material/Materials.xlsx
+++ b/doc/Material/Materials.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dd3204\Projets\spartacus\doc\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381526CB-0FD3-40AE-99DF-5779B1BBFEE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D96EB52-B28B-4E6C-AE10-42357E74BCAA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{284EAF35-2C3A-44EE-A254-267BE16E4CFD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{284EAF35-2C3A-44EE-A254-267BE16E4CFD}"/>
   </bookViews>
   <sheets>
     <sheet name="PolynomialMP" sheetId="1" r:id="rId1"/>
-    <sheet name="Fluage" sheetId="2" r:id="rId2"/>
+    <sheet name="Feuil1" sheetId="3" r:id="rId2"/>
+    <sheet name="Fluage" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -878,49 +879,49 @@
                   <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7500000000000001E-2</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.4999999999999998E-2</c:v>
+                  <c:v>0.03</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.2500000000000003E-2</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.04</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.7499999999999999E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.5000000000000003E-2</c:v>
+                  <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.2500000000000001E-2</c:v>
+                  <c:v>-0.02</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.03</c:v>
+                  <c:v>-0.03</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.75E-2</c:v>
+                  <c:v>-0.04</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.5000000000000001E-2</c:v>
+                  <c:v>-0.05</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.2499999999999999E-2</c:v>
+                  <c:v>-0.06</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.02</c:v>
+                  <c:v>-7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.7500000000000002E-2</c:v>
+                  <c:v>-0.08</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.4999999999999999E-2</c:v>
+                  <c:v>-0.09</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.2500000000000001E-2</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -938,49 +939,49 @@
                   <c:v>344414065.52125406</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>319414066.9069171</c:v>
+                  <c:v>244414110.17265934</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>294414071.07883608</c:v>
+                  <c:v>144415134.55947912</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>269414082.34547812</c:v>
+                  <c:v>44426514.79971379</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>244414110.17265934</c:v>
+                  <c:v>-55493497.644596696</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>219414173.95922709</c:v>
+                  <c:v>-155083690.81634748</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>194414311.20500267</c:v>
+                  <c:v>-253427811.78019178</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>169414590.88598746</c:v>
+                  <c:v>-347952101.5870856</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>144415134.55947912</c:v>
+                  <c:v>-433127855.8412925</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>119416148.61819392</c:v>
+                  <c:v>-501135649.27375972</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>94417972.226878941</c:v>
+                  <c:v>-547119774.31966186</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>69421146.835933387</c:v>
+                  <c:v>-573665999.10817599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>44426514.79971379</c:v>
+                  <c:v>-587525852.99485302</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19435356.549590826</c:v>
+                  <c:v>-594490993.7397871</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-5550422.0166032314</c:v>
+                  <c:v>-597998223.57282162</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-30528037.798635125</c:v>
+                  <c:v>-599802284.29206276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1026,82 +1027,82 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>1.2500000000000001E-2</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7500000000000002E-2</c:v>
+                  <c:v>-0.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.2500000000000003E-2</c:v>
+                  <c:v>-0.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7500000000000004E-2</c:v>
+                  <c:v>-7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2500000000000001E-2</c:v>
+                  <c:v>-0.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.7499999999999999E-2</c:v>
+                  <c:v>-0.05</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.2499999999999996E-2</c:v>
+                  <c:v>-0.04</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.7499999999999994E-2</c:v>
+                  <c:v>-0.03</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.2499999999999991E-2</c:v>
+                  <c:v>-0.02</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.7499999999999989E-2</c:v>
+                  <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.2499999999999986E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.7499999999999991E-2</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.2499999999999995E-2</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.7499999999999999E-2</c:v>
+                  <c:v>0.03</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.2500000000000004E-2</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.7500000000000008E-2</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.2500000000000013E-2</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.7500000000000017E-2</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.10250000000000002</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.10750000000000003</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.11250000000000003</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.11750000000000003</c:v>
+                  <c:v>0.11</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.12250000000000004</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.12750000000000003</c:v>
+                  <c:v>0.13</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.13250000000000003</c:v>
+                  <c:v>0.14000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.13750000000000004</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1113,82 +1114,82 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>-30528037.798635125</c:v>
+                  <c:v>-599802284.29206276</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19471962.201325789</c:v>
+                  <c:v>-499802284.29222757</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>69471962.12126635</c:v>
+                  <c:v>-399802284.62967199</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>119471955.27303609</c:v>
+                  <c:v>-299802313.49442136</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>169471798.1602616</c:v>
+                  <c:v>-199802975.70898545</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>219470052.58560053</c:v>
+                  <c:v>-99810332.78696847</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>269457776.79406911</c:v>
+                  <c:v>137943.1088937521</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>319394724.69166654</c:v>
+                  <c:v>99872616.796319842</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>369137598.8345477</c:v>
+                  <c:v>198795748.54443049</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>418263291.07921106</c:v>
+                  <c:v>295186915.33786786</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>465725547.9932934</c:v>
+                  <c:v>385094826.70902002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>509437540.79401934</c:v>
+                  <c:v>461951668.29158235</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>546383407.7548424</c:v>
+                  <c:v>519515128.51541018</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>574098659.69245005</c:v>
+                  <c:v>557008967.30162811</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>592555627.71506476</c:v>
+                  <c:v>579362382.05076861</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>603965310.49540842</c:v>
+                  <c:v>592611117.94308758</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>610966011.32229817</c:v>
+                  <c:v>601010307.74188113</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>615494289.28526974</c:v>
+                  <c:v>606940855.45854115</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>618697553.33110619</c:v>
+                  <c:v>611618734.88675141</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>621196231.31901205</c:v>
+                  <c:v>615650333.62493801</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>623316035.19453931</c:v>
+                  <c:v>619340205.67682481</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>625228068.11751103</c:v>
+                  <c:v>622844452.17179632</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>627023536.62821853</c:v>
+                  <c:v>626245129.1861062</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>628752066.09591496</c:v>
+                  <c:v>629586522.61587477</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>630441272.3273927</c:v>
+                  <c:v>632893158.29655313</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>632106874.93801749</c:v>
+                  <c:v>636178956.03475118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1388,6 +1389,653 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$2:$A$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.03</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.02</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.04</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.06</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.08</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.08</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.06</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.02</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.02</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.04</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.06</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.08</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.12</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.14000000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$B$2:$B$62</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>-102000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-200004000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-200106000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-200208000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-200310000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-200412000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-200514000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-514021</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>199444000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>395964000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>543647000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>590580000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>602817000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>610145000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>613472000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>619963000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>419963000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>219993000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22471000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-136433000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-195286000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-210058000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-217815000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-224491000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-230959000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-237379000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-37378900</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>162591000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>360114000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>519028000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>577893000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>592668000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>392668000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>192709000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-3879530</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-152270000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-199853000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-212217000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-219566000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-226158000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F05D-4115-90C4-9B204C9A92F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$D$2:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$E$2:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98210937.797000006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>190000001.02399999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>276070314.41100001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>356000002.68800002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>428554690.625</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>492000003.07200003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>544414064.99900007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>584000001.53600001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>609398438.01300001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>619999999.99999976</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F05D-4115-90C4-9B204C9A92F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="665295856"/>
+        <c:axId val="665809416"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="665295856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665809416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="665809416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665295856"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -1968,6 +2616,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3001,6 +3689,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3594,6 +4798,47 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>388882</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>153386</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>328447</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>177362</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6D39A39-C219-41B4-93B9-922B8B6F1238}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4346,7 +5591,7 @@
       </c>
       <c r="G46">
         <f>A68</f>
-        <v>1.2500000000000001E-2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -4362,7 +5607,7 @@
       </c>
       <c r="G47" s="1">
         <f>D68</f>
-        <v>-30528037.798635125</v>
+        <v>-599802284.29206276</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -4378,7 +5623,7 @@
       </c>
       <c r="G48" s="1">
         <f>(G47-B43-G46*B37+B42*B38)/(B38-B37)</f>
-        <v>7.6798763596758121E-2</v>
+        <v>1.9359409229153732E-2</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -4394,7 +5639,7 @@
       </c>
       <c r="G49" s="1">
         <f>G47-(G46-G48)*B37</f>
-        <v>612459598.16894615</v>
+        <v>593791807.99947453</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -4439,7 +5684,7 @@
       </c>
       <c r="F52">
         <f>A68</f>
-        <v>1.2500000000000001E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="G52" s="1">
         <f>(F52-$G$46)/($G$48-$G$46)</f>
@@ -4451,7 +5696,7 @@
       </c>
       <c r="I52" s="1">
         <f>D68</f>
-        <v>-30528037.798635125</v>
+        <v>-599802284.29206276</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -4471,685 +5716,660 @@
         <v>344414065.52125406</v>
       </c>
       <c r="F53">
-        <f>F52+0.005</f>
-        <v>1.7500000000000002E-2</v>
+        <v>-0.09</v>
       </c>
       <c r="G53" s="1">
         <f t="shared" ref="G53:G77" si="4">(F53-$G$46)/($G$48-$G$46)</f>
-        <v>7.7761992926596427E-2</v>
+        <v>8.3780575528833057E-2</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" ref="H53:H77" si="5">$B$44*G53+((1-$B$44)*G53)/(1+G53^$B$39)^(1/$B$39)</f>
-        <v>7.7761992926535614E-2</v>
+        <v>8.3780575528694931E-2</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" ref="I53:I77" si="6">H53*($G$49-$G$47)+$G$47</f>
-        <v>19471962.201325789</v>
+        <v>-499802284.29222757</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>4.7500000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="B54" s="1">
         <f t="shared" ref="B54:B68" si="7">(A54-$B$46)/($B$48-$B$46)</f>
-        <v>0.19626266922035238</v>
+        <v>0.2616835589604698</v>
       </c>
       <c r="C54" s="1">
         <f t="shared" ref="C54:C68" si="8">($B$44*B54+(1-$B$44)*B54)/(1+B54^$B$39)^(1/$B$39)</f>
-        <v>0.19626266755611724</v>
+        <v>0.26168351955645669</v>
       </c>
       <c r="D54" s="1">
         <f t="shared" ref="D54:D68" si="9">C54*($B$49-$B$47)+$B$47</f>
-        <v>319414066.9069171</v>
+        <v>244414110.17265934</v>
       </c>
       <c r="F54">
-        <f t="shared" ref="F54:F77" si="10">F53+0.005</f>
-        <v>2.2500000000000003E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="4"/>
-        <v>0.15552398585319285</v>
+        <v>0.167561151057666</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="5"/>
-        <v>0.15552398572862039</v>
+        <v>0.16756115077481504</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="6"/>
-        <v>69471962.12126635</v>
+        <v>-399802284.62967199</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>4.4999999999999998E-2</v>
+        <v>0.03</v>
       </c>
       <c r="B55" s="1">
         <f t="shared" si="7"/>
-        <v>0.21806963246705818</v>
+        <v>0.34891141194729308</v>
       </c>
       <c r="C55" s="1">
         <f t="shared" si="8"/>
-        <v>0.21806962716374775</v>
+        <v>0.34891047899265076</v>
       </c>
       <c r="D55" s="1">
         <f t="shared" si="9"/>
-        <v>294414071.07883608</v>
+        <v>144415134.55947912</v>
       </c>
       <c r="F55">
-        <f t="shared" si="10"/>
-        <v>2.7500000000000004E-2</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="G55" s="1">
         <f t="shared" si="4"/>
-        <v>0.23328597877978927</v>
+        <v>0.25134172658649895</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="5"/>
-        <v>0.23328596800457616</v>
+        <v>0.25134170212059487</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="6"/>
-        <v>119471955.27303609</v>
+        <v>-299802313.49442136</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>4.2500000000000003E-2</v>
+        <v>0.02</v>
       </c>
       <c r="B56" s="1">
         <f t="shared" si="7"/>
-        <v>0.23987659571376396</v>
+        <v>0.43613926493411626</v>
       </c>
       <c r="C56" s="1">
         <f t="shared" si="8"/>
-        <v>0.23987658058280359</v>
+        <v>0.43612840524025259</v>
       </c>
       <c r="D56" s="1">
         <f t="shared" si="9"/>
-        <v>269414082.34547812</v>
+        <v>44426514.79971379</v>
       </c>
       <c r="F56">
-        <f t="shared" si="10"/>
-        <v>3.2500000000000001E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="G56" s="1">
         <f t="shared" si="4"/>
-        <v>0.31104797170638565</v>
+        <v>0.335122302115332</v>
       </c>
       <c r="H56" s="1">
         <f t="shared" si="5"/>
-        <v>0.31104771658312336</v>
+        <v>0.33512172284225483</v>
       </c>
       <c r="I56" s="1">
         <f t="shared" si="6"/>
-        <v>169471798.1602616</v>
+        <v>-199802975.70898545</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="B57" s="1">
         <f t="shared" si="7"/>
-        <v>0.2616835589604698</v>
+        <v>0.52336711792093948</v>
       </c>
       <c r="C57" s="1">
         <f t="shared" si="8"/>
-        <v>0.26168351955645669</v>
+        <v>0.52328648679959122</v>
       </c>
       <c r="D57" s="1">
         <f t="shared" si="9"/>
-        <v>244414110.17265934</v>
+        <v>-55493497.644596696</v>
       </c>
       <c r="F57">
-        <f t="shared" si="10"/>
-        <v>3.7499999999999999E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="G57" s="1">
         <f t="shared" si="4"/>
-        <v>0.38880996463298201</v>
+        <v>0.41890287764416495</v>
       </c>
       <c r="H57" s="1">
         <f t="shared" si="5"/>
-        <v>0.38880699472243085</v>
+        <v>0.41889613456881158</v>
       </c>
       <c r="I57" s="1">
         <f t="shared" si="6"/>
-        <v>219470052.58560053</v>
+        <v>-99810332.78696847</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>3.7499999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="B58" s="1">
         <f t="shared" si="7"/>
-        <v>0.28349052220717563</v>
+        <v>0.61059497090776282</v>
       </c>
       <c r="C58" s="1">
         <f t="shared" si="8"/>
-        <v>0.28349042716350897</v>
+        <v>0.61015687408873931</v>
       </c>
       <c r="D58" s="1">
         <f t="shared" si="9"/>
-        <v>219414173.95922709</v>
+        <v>-155083690.81634748</v>
       </c>
       <c r="F58">
-        <f t="shared" si="10"/>
-        <v>4.2499999999999996E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="G58" s="1">
         <f t="shared" si="4"/>
-        <v>0.46657195755957837</v>
+        <v>0.50268345317299801</v>
       </c>
       <c r="H58" s="1">
         <f t="shared" si="5"/>
-        <v>0.46654989584874251</v>
+        <v>0.50263337534551078</v>
       </c>
       <c r="I58" s="1">
         <f t="shared" si="6"/>
-        <v>269457776.79406911</v>
+        <v>137943.1088937521</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>3.5000000000000003E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="B59" s="1">
         <f t="shared" si="7"/>
-        <v>0.30529748545388141</v>
+        <v>0.69782282389458605</v>
       </c>
       <c r="C59" s="1">
         <f t="shared" si="8"/>
-        <v>0.30529727069367141</v>
+        <v>0.69594033934426502</v>
       </c>
       <c r="D59" s="1">
         <f t="shared" si="9"/>
-        <v>194414311.20500267</v>
+        <v>-253427811.78019178</v>
       </c>
       <c r="F59">
-        <f t="shared" si="10"/>
-        <v>4.7499999999999994E-2</v>
+        <v>-0.03</v>
       </c>
       <c r="G59" s="1">
         <f t="shared" si="4"/>
-        <v>0.54433395048617472</v>
+        <v>0.58646402870183101</v>
       </c>
       <c r="H59" s="1">
         <f t="shared" si="5"/>
-        <v>0.54421382763251824</v>
+        <v>0.58619165896263992</v>
       </c>
       <c r="I59" s="1">
         <f t="shared" si="6"/>
-        <v>319394724.69166654</v>
+        <v>99872616.796319842</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>3.2500000000000001E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="B60" s="1">
         <f t="shared" si="7"/>
-        <v>0.32710444870058725</v>
+        <v>0.78505067688140928</v>
       </c>
       <c r="C60" s="1">
         <f t="shared" si="8"/>
-        <v>0.32710398998065898</v>
+        <v>0.77839184789386118</v>
       </c>
       <c r="D60" s="1">
         <f t="shared" si="9"/>
-        <v>169414590.88598746</v>
+        <v>-347952101.5870856</v>
       </c>
       <c r="F60">
-        <f t="shared" si="10"/>
-        <v>5.2499999999999991E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="G60" s="1">
         <f t="shared" si="4"/>
-        <v>0.62209594341277119</v>
+        <v>0.6702446042306639</v>
       </c>
       <c r="H60" s="1">
         <f t="shared" si="5"/>
-        <v>0.62157592817746421</v>
+        <v>0.66907002807235272</v>
       </c>
       <c r="I60" s="1">
         <f t="shared" si="6"/>
-        <v>369137598.8345477</v>
+        <v>198795748.54443049</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="B61" s="1">
         <f t="shared" si="7"/>
-        <v>0.34891141194729308</v>
+        <v>0.87227852986823251</v>
       </c>
       <c r="C61" s="1">
         <f t="shared" si="8"/>
-        <v>0.34891047899265076</v>
+        <v>0.85268882959513859</v>
       </c>
       <c r="D61" s="1">
         <f t="shared" si="9"/>
-        <v>144415134.55947912</v>
+        <v>-433127855.8412925</v>
       </c>
       <c r="F61">
-        <f t="shared" si="10"/>
-        <v>5.7499999999999989E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="G61" s="1">
         <f t="shared" si="4"/>
-        <v>0.69985793633936744</v>
+        <v>0.75402517975949701</v>
       </c>
       <c r="H61" s="1">
         <f t="shared" si="5"/>
-        <v>0.69797816283433756</v>
+        <v>0.74982710237085193</v>
       </c>
       <c r="I61" s="1">
         <f t="shared" si="6"/>
-        <v>418263291.07921106</v>
+        <v>295186915.33786786</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>2.75E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="B62" s="1">
         <f t="shared" si="7"/>
-        <v>0.37071837519399892</v>
+        <v>0.95950638285505585</v>
       </c>
       <c r="C62" s="1">
         <f t="shared" si="8"/>
-        <v>0.37071655769771161</v>
+        <v>0.91201056766999355</v>
       </c>
       <c r="D62" s="1">
         <f t="shared" si="9"/>
-        <v>119416148.61819392</v>
+        <v>-501135649.27375972</v>
       </c>
       <c r="F62">
-        <f t="shared" si="10"/>
-        <v>6.2499999999999986E-2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
         <f t="shared" si="4"/>
-        <v>0.77761992926596391</v>
+        <v>0.8378057552883299</v>
       </c>
       <c r="H62" s="1">
         <f t="shared" si="5"/>
-        <v>0.77179335656300097</v>
+        <v>0.82515246796355635</v>
       </c>
       <c r="I62" s="1">
         <f t="shared" si="6"/>
-        <v>465725547.9932934</v>
+        <v>385094826.70902002</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>2.5000000000000001E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="B63" s="1">
         <f t="shared" si="7"/>
-        <v>0.39252533844070464</v>
+        <v>1.046734235841879</v>
       </c>
       <c r="C63" s="1">
         <f>($B$44*B63+(1-$B$44)*B63)/(1+B63^$B$39)^(1/$B$39)</f>
-        <v>0.3925219302497146</v>
+        <v>0.95212153266231003</v>
       </c>
       <c r="D63" s="1">
         <f t="shared" si="9"/>
-        <v>94417972.226878941</v>
+        <v>-547119774.31966186</v>
       </c>
       <c r="F63">
-        <f t="shared" si="10"/>
-        <v>6.7499999999999991E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G63" s="1">
         <f t="shared" si="4"/>
-        <v>0.85538192219256037</v>
+        <v>0.9215863308171629</v>
       </c>
       <c r="H63" s="1">
         <f t="shared" si="5"/>
-        <v>0.83977599006255066</v>
+        <v>0.88954357217471047</v>
       </c>
       <c r="I63" s="1">
         <f t="shared" si="6"/>
-        <v>509437540.79401934</v>
+        <v>461951668.29158235</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>2.2499999999999999E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="B64" s="1">
         <f t="shared" si="7"/>
-        <v>0.41433230168741048</v>
+        <v>1.1339620888287023</v>
       </c>
       <c r="C64" s="1">
         <f t="shared" si="8"/>
-        <v>0.41432612435310151</v>
+        <v>0.97527723459438675</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="9"/>
-        <v>69421146.835933387</v>
+        <v>-573665999.10817599</v>
       </c>
       <c r="F64">
-        <f t="shared" si="10"/>
-        <v>7.2499999999999995E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G64" s="1">
         <f t="shared" si="4"/>
-        <v>0.93314391511915684</v>
+        <v>1.005366906345996</v>
       </c>
       <c r="H64" s="1">
         <f t="shared" si="5"/>
-        <v>0.89723567496804058</v>
+        <v>0.93777057044454437</v>
       </c>
       <c r="I64" s="1">
         <f t="shared" si="6"/>
-        <v>546383407.7548424</v>
+        <v>519515128.51541018</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>0.02</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="B65" s="1">
         <f t="shared" si="7"/>
-        <v>0.43613926493411626</v>
+        <v>1.2211899418155256</v>
       </c>
       <c r="C65" s="1">
         <f t="shared" si="8"/>
-        <v>0.43612840524025259</v>
+        <v>0.98736688756684587</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="9"/>
-        <v>44426514.79971379</v>
+        <v>-587525852.99485302</v>
       </c>
       <c r="F65">
-        <f t="shared" si="10"/>
-        <v>7.7499999999999999E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G65" s="1">
         <f t="shared" si="4"/>
-        <v>1.0109059080457534</v>
+        <v>1.0891474818748288</v>
       </c>
       <c r="H65" s="1">
         <f t="shared" si="5"/>
-        <v>0.94033953947066218</v>
+        <v>0.96918312436749043</v>
       </c>
       <c r="I65" s="1">
         <f t="shared" si="6"/>
-        <v>574098659.69245005</v>
+        <v>557008967.30162811</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>1.7500000000000002E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="B66" s="1">
         <f t="shared" si="7"/>
-        <v>0.45794622818082209</v>
+        <v>1.308417794802349</v>
       </c>
       <c r="C66" s="1">
         <f t="shared" si="8"/>
-        <v>0.45792765601837421</v>
+        <v>0.99344243029616242</v>
       </c>
       <c r="D66" s="1">
         <f t="shared" si="9"/>
-        <v>19435356.549590826</v>
+        <v>-594490993.7397871</v>
       </c>
       <c r="F66">
-        <f t="shared" si="10"/>
-        <v>8.2500000000000004E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G66" s="1">
         <f t="shared" si="4"/>
-        <v>1.0886679009723499</v>
+        <v>1.172928057403662</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="5"/>
-        <v>0.96904455180708193</v>
+        <v>0.98791094389466738</v>
       </c>
       <c r="I66" s="1">
         <f t="shared" si="6"/>
-        <v>592555627.71506476</v>
+        <v>579362382.05076861</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>-0.09</v>
       </c>
       <c r="B67" s="1">
         <f t="shared" si="7"/>
-        <v>0.47975319142752793</v>
+        <v>1.3956456477891721</v>
       </c>
       <c r="C67" s="1">
         <f t="shared" si="8"/>
-        <v>0.47972221421370714</v>
+        <v>0.99650171157883172</v>
       </c>
       <c r="D67" s="1">
         <f t="shared" si="9"/>
-        <v>-5550422.0166032314</v>
+        <v>-597998223.57282162</v>
       </c>
       <c r="F67">
-        <f t="shared" si="10"/>
-        <v>8.7500000000000008E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G67" s="1">
         <f t="shared" si="4"/>
-        <v>1.1664298938989464</v>
+        <v>1.256708632932495</v>
       </c>
       <c r="H67" s="1">
         <f t="shared" si="5"/>
-        <v>0.98678934524027773</v>
+        <v>0.99901081107554734</v>
       </c>
       <c r="I67" s="1">
         <f t="shared" si="6"/>
-        <v>603965310.49540842</v>
+        <v>592611117.94308758</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>1.2500000000000001E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="B68" s="1">
         <f t="shared" si="7"/>
-        <v>0.50156015467423376</v>
+        <v>1.4828735007759954</v>
       </c>
       <c r="C68" s="1">
         <f t="shared" si="8"/>
-        <v>0.50150965218767152</v>
+        <v>0.99807535501080435</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="9"/>
-        <v>-30528037.798635125</v>
+        <f>C68*($B$49-$B$47)+$B$47</f>
+        <v>-599802284.29206276</v>
       </c>
       <c r="F68">
-        <f t="shared" si="10"/>
-        <v>9.2500000000000013E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G68" s="1">
         <f t="shared" si="4"/>
-        <v>1.2441918868255428</v>
+        <v>1.3404892084613278</v>
       </c>
       <c r="H68" s="1">
         <f t="shared" si="5"/>
-        <v>0.99767711420391403</v>
+        <v>1.0060477006287356</v>
       </c>
       <c r="I68" s="1">
         <f t="shared" si="6"/>
-        <v>610966011.32229817</v>
+        <v>601010307.74188113</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
       <c r="F69">
-        <f t="shared" si="10"/>
-        <v>9.7500000000000017E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G69" s="1">
         <f t="shared" si="4"/>
-        <v>1.3219538797521393</v>
+        <v>1.424269783990161</v>
       </c>
       <c r="H69" s="1">
         <f t="shared" si="5"/>
-        <v>1.0047196725824392</v>
+        <v>1.0110163476377654</v>
       </c>
       <c r="I69" s="1">
         <f t="shared" si="6"/>
-        <v>615494289.28526974</v>
+        <v>606940855.45854115</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
       <c r="F70">
-        <f t="shared" si="10"/>
-        <v>0.10250000000000002</v>
+        <v>0.08</v>
       </c>
       <c r="G70" s="1">
         <f t="shared" si="4"/>
-        <v>1.3997158726787358</v>
+        <v>1.5080503595189938</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="5"/>
-        <v>1.0097015165039263</v>
+        <v>1.0149355019452648</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="6"/>
-        <v>618697553.33110619</v>
+        <v>611618734.88675141</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
       <c r="F71">
-        <f t="shared" si="10"/>
-        <v>0.10750000000000003</v>
+        <v>0.09</v>
       </c>
       <c r="G71" s="1">
         <f t="shared" si="4"/>
-        <v>1.4774778656053322</v>
+        <v>1.5918309350478268</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" si="5"/>
-        <v>1.0135875601043538</v>
+        <v>1.0183131985711307</v>
       </c>
       <c r="I71" s="1">
         <f t="shared" si="6"/>
-        <v>621196231.31901205</v>
+        <v>615650333.62493801</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
       <c r="F72">
-        <f t="shared" si="10"/>
-        <v>0.11250000000000003</v>
+        <v>0.1</v>
       </c>
       <c r="G72" s="1">
         <f t="shared" si="4"/>
-        <v>1.5552398585319287</v>
+        <v>1.6756115105766598</v>
       </c>
       <c r="H72" s="1">
         <f t="shared" si="5"/>
-        <v>1.0168843635838443</v>
+        <v>1.021404594612479</v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="6"/>
-        <v>623316035.19453931</v>
+        <v>619340205.67682481</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
       <c r="F73">
-        <f t="shared" si="10"/>
-        <v>0.11750000000000003</v>
+        <v>0.11</v>
       </c>
       <c r="G73" s="1">
         <f t="shared" si="4"/>
-        <v>1.6330018514585252</v>
+        <v>1.759392086105493</v>
       </c>
       <c r="H73" s="1">
         <f t="shared" si="5"/>
-        <v>1.0198580333964753</v>
+        <v>1.0243404724939151</v>
       </c>
       <c r="I73" s="1">
         <f t="shared" si="6"/>
-        <v>625228068.11751103</v>
+        <v>622844452.17179632</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
       <c r="F74">
-        <f t="shared" si="10"/>
-        <v>0.12250000000000004</v>
+        <v>0.12</v>
       </c>
       <c r="G74" s="1">
         <f t="shared" si="4"/>
-        <v>1.7107638443851216</v>
+        <v>1.8431726616343258</v>
       </c>
       <c r="H74" s="1">
         <f t="shared" si="5"/>
-        <v>1.0226504175890665</v>
+        <v>1.0271895792683807</v>
       </c>
       <c r="I74" s="1">
         <f t="shared" si="6"/>
-        <v>627023536.62821853</v>
+        <v>626245129.1861062</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B75" s="1"/>
       <c r="F75">
-        <f t="shared" si="10"/>
-        <v>0.12750000000000003</v>
+        <v>0.13</v>
       </c>
       <c r="G75" s="1">
         <f t="shared" si="4"/>
-        <v>1.7885258373117179</v>
+        <v>1.9269532371631588</v>
       </c>
       <c r="H75" s="1">
         <f t="shared" si="5"/>
-        <v>1.025338695513875</v>
+        <v>1.0299890179145235</v>
       </c>
       <c r="I75" s="1">
         <f t="shared" si="6"/>
-        <v>628752066.09591496</v>
+        <v>629586522.61587477</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B76" s="1"/>
       <c r="F76">
-        <f t="shared" si="10"/>
-        <v>0.13250000000000003</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G76" s="1">
         <f t="shared" si="4"/>
-        <v>1.8662878302383143</v>
+        <v>2.010733812691992</v>
       </c>
       <c r="H76" s="1">
         <f t="shared" si="5"/>
-        <v>1.0279658163743497</v>
+        <v>1.0327593363184375</v>
       </c>
       <c r="I76" s="1">
         <f t="shared" si="6"/>
-        <v>630441272.3273927</v>
+        <v>632893158.29655313</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F77">
-        <f t="shared" si="10"/>
-        <v>0.13750000000000004</v>
+        <v>0.15</v>
       </c>
       <c r="G77" s="1">
         <f t="shared" si="4"/>
-        <v>1.9440498231649106</v>
+        <v>2.0945143882208246</v>
       </c>
       <c r="H77" s="1">
         <f t="shared" si="5"/>
-        <v>1.0305562279428682</v>
+        <v>1.0355121965742131</v>
       </c>
       <c r="I77" s="1">
         <f t="shared" si="6"/>
-        <v>632106874.93801749</v>
+        <v>636178956.03475118</v>
       </c>
     </row>
   </sheetData>
@@ -5160,6 +6380,469 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9085128-8255-4C3C-8900-F73A451DACB0}">
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>-0.01</v>
+      </c>
+      <c r="B2" s="1">
+        <v>-102000000</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>-0.02</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-200004000</v>
+      </c>
+      <c r="D3">
+        <v>0.01</v>
+      </c>
+      <c r="E3">
+        <v>98210937.797000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>-0.03</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-200106000</v>
+      </c>
+      <c r="D4">
+        <v>0.02</v>
+      </c>
+      <c r="E4">
+        <v>190000001.02399999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>-0.04</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-200208000</v>
+      </c>
+      <c r="D5">
+        <v>0.03</v>
+      </c>
+      <c r="E5">
+        <v>276070314.41100001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>-0.05</v>
+      </c>
+      <c r="B6" s="1">
+        <v>-200310000</v>
+      </c>
+      <c r="D6">
+        <v>0.04</v>
+      </c>
+      <c r="E6">
+        <v>356000002.68800002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>-0.06</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-200412000</v>
+      </c>
+      <c r="D7">
+        <v>0.05</v>
+      </c>
+      <c r="E7">
+        <v>428554690.625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>-200514000</v>
+      </c>
+      <c r="D8">
+        <v>0.06</v>
+      </c>
+      <c r="E8">
+        <v>492000003.07200003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-0.05</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-514021</v>
+      </c>
+      <c r="D9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E9">
+        <v>544414064.99900007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>-0.03</v>
+      </c>
+      <c r="B10" s="1">
+        <v>199444000</v>
+      </c>
+      <c r="D10">
+        <v>0.08</v>
+      </c>
+      <c r="E10">
+        <v>584000001.53600001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>-0.01</v>
+      </c>
+      <c r="B11" s="1">
+        <v>395964000</v>
+      </c>
+      <c r="D11">
+        <v>0.09</v>
+      </c>
+      <c r="E11">
+        <v>609398438.01300001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.01</v>
+      </c>
+      <c r="B12" s="1">
+        <v>543647000</v>
+      </c>
+      <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="E12">
+        <v>619999999.99999976</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.03</v>
+      </c>
+      <c r="B13" s="1">
+        <v>590580000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.05</v>
+      </c>
+      <c r="B14" s="1">
+        <v>602817000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B15" s="1">
+        <v>610145000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.08</v>
+      </c>
+      <c r="B16" s="1">
+        <v>613472000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.1</v>
+      </c>
+      <c r="B17" s="1">
+        <v>619963000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.08</v>
+      </c>
+      <c r="B18" s="1">
+        <v>419963000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0.06</v>
+      </c>
+      <c r="B19" s="1">
+        <v>219993000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.04</v>
+      </c>
+      <c r="B20" s="1">
+        <v>22471000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.02</v>
+      </c>
+      <c r="B21" s="1">
+        <v>-136433000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-195286000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>-0.02</v>
+      </c>
+      <c r="B23" s="1">
+        <v>-210058000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>-0.04</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-217815000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>-0.06</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-224491000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>-0.08</v>
+      </c>
+      <c r="B26" s="1">
+        <v>-230959000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>-0.1</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-237379000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>-0.08</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-37378900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>-0.06</v>
+      </c>
+      <c r="B29" s="1">
+        <v>162591000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>-0.04</v>
+      </c>
+      <c r="B30" s="1">
+        <v>360114000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>-0.02</v>
+      </c>
+      <c r="B31" s="1">
+        <v>519028000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1">
+        <v>577893000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>0.02</v>
+      </c>
+      <c r="B33" s="1">
+        <v>592668000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1">
+        <v>392668000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>-0.02</v>
+      </c>
+      <c r="B35" s="1">
+        <v>192709000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>-0.04</v>
+      </c>
+      <c r="B36" s="1">
+        <v>-3879530</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>-0.06</v>
+      </c>
+      <c r="B37" s="1">
+        <v>-152270000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>-0.08</v>
+      </c>
+      <c r="B38" s="1">
+        <v>-199853000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>-0.1</v>
+      </c>
+      <c r="B39" s="1">
+        <v>-212217000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>-0.12</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-219566000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="B41" s="1">
+        <v>-226158000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="1"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="1"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="1"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="1"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="1"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="1"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="1"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="1"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D273388-FAD7-4340-844A-9B82C7B3ECA5}">
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
